--- a/dist/denki-estimate-invoice.xlsx
+++ b/dist/denki-estimate-invoice.xlsx
@@ -1477,7 +1477,7 @@
       </c>
       <c r="F35" s="19" t="n"/>
       <c r="G35" s="20">
-        <f>ROUNDDOWN(G34*自社情報!$B$16,0)</f>
+        <f>IF(N(自社情報!$B$16)&lt;=0,"税率未入力",ROUNDDOWN(G34*自社情報!$B$16,0))</f>
         <v/>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F36" s="19" t="n"/>
       <c r="G36" s="20">
-        <f>G34+G35</f>
+        <f>IF(ISNUMBER(G35),G34+G35,"税率未入力")</f>
         <v/>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="F41" s="19" t="n"/>
       <c r="G41" s="20">
-        <f>ROUNDDOWN(G40*自社情報!$B$16,0)</f>
+        <f>IF(N(自社情報!$B$16)&lt;=0,"税率未入力",ROUNDDOWN(G40*自社情報!$B$16,0))</f>
         <v/>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="F42" s="19" t="n"/>
       <c r="G42" s="20">
-        <f>G40+G41</f>
+        <f>IF(ISNUMBER(G41),G40+G41,"税率未入力")</f>
         <v/>
       </c>
     </row>
